--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4980-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4980-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6F0D395-E5E1-4DAC-A68D-4D05E7F25E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0C23CFE-D841-43C9-B301-CA856B39F59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{9F1F4675-5248-4A1F-BF3C-BE4000CECC34}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{53096A7B-C1B6-4556-BB52-DF0005805F93}"/>
   </bookViews>
   <sheets>
     <sheet name="4980-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1445,25 +1445,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D251FC01-B269-4F2E-8152-E6BA818D9465}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444E4538-89B6-4D38-9B9C-4A2399803580}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1491,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1521,7 +1521,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1617,7 +1617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="39">
         <v>2022</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>26</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2021</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2020</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2019</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2018</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2017</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2016</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2015</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2014</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2013</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2012</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2011</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>34</v>
       </c>
